--- a/uploads/excel/Active_Work_Orders_7-7-2026_4-46-51_PM.xlsx
+++ b/uploads/excel/Active_Work_Orders_7-7-2026_4-46-51_PM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibm-my.sharepoint.com/personal/miftah_choiri_ibm_com/Documents/IBM💼/PROJECTS🎯/OPPORTUNITY/LENOVO-REPORT/mba Devi/REPORT ONSITE - mba devi/new-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mifta\Desktop\devi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{FFE073FD-A671-496F-8029-D2DA650E922E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FAE746B-91F6-4C1B-9ACA-1622EC69C7FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1BFF98-CD90-4F96-AD16-9C438E124ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="38580" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2730" windowWidth="51600" windowHeight="16725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Active Work Orders" sheetId="1" r:id="rId1"/>
@@ -52710,7 +52710,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB518" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB518">
     <sortCondition ref="W1"/>
   </sortState>
